--- a/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
+++ b/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Nachlassverzeichnis" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Ertragsberechnung" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Erbschaftssteuer Hille" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -509,4 +510,22 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
+++ b/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Nachlassverzeichnis" sheetId="1" state="visible" r:id="rId3"/>

--- a/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
+++ b/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
@@ -89,10 +89,10 @@
     <t xml:space="preserve">Fisher Depot Managementgebühren Q1+Q2</t>
   </si>
   <si>
-    <t xml:space="preserve">(geschätzt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erträge 2026</t>
+    <t xml:space="preserve">(geschätzt wie 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erträge 2026 1.1-30.9. </t>
   </si>
   <si>
     <t xml:space="preserve">Summe Einnahmen 25</t>
@@ -252,7 +252,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -270,10 +270,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -518,22 +514,13 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="3" t="n">
         <f aca="false">SUM(B14:B17)</f>
         <v>3484.02</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -555,21 +542,18 @@
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>1413</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="3" t="n">
         <f aca="false">SUM(B22:B25)</f>
         <v>6127.65</v>
       </c>
@@ -593,9 +577,9 @@
   <dimension ref="A1:G200"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24.29"/>
   </cols>
   <sheetData>
@@ -606,7 +590,7 @@
       <c r="B1" s="4" t="n">
         <v>23548.63</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -617,31 +601,30 @@
       <c r="B2" s="4" t="n">
         <v>-6558.25</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>3458.18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>3874.27</v>
       </c>
       <c r="G3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>3460.27</v>
       </c>
       <c r="G4" s="4"/>
@@ -658,25 +641,19 @@
       <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>3903.26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">SUM(E2:E5)</f>
         <v>14695.98</v>
       </c>
-      <c r="F6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="F7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -689,10 +666,9 @@
       <c r="D8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>3874.27</v>
       </c>
-      <c r="F8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -705,27 +681,23 @@
       <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>3913.38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <f aca="false">SUM(E8:E9)</f>
         <v>7787.65</v>
       </c>
-      <c r="F10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
+      <c r="A11" s="6"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="F11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -736,943 +708,752 @@
         <v>12502.3</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="F12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
       <c r="B14" s="3"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
+      <c r="A15" s="6"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
+      <c r="A16" s="6"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
+      <c r="A17" s="6"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
+      <c r="A18" s="6"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
+      <c r="A19" s="6"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
+      <c r="A20" s="6"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
+      <c r="A21" s="6"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
+      <c r="A22" s="6"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
+      <c r="A23" s="6"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
+      <c r="A24" s="6"/>
       <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
+      <c r="A25" s="6"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
+      <c r="A26" s="6"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
+      <c r="A27" s="6"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
+      <c r="A28" s="6"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
+      <c r="A29" s="6"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
+      <c r="A30" s="6"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
+      <c r="A31" s="6"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
+      <c r="A32" s="6"/>
       <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
+      <c r="A33" s="6"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
+      <c r="A34" s="6"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
+      <c r="A35" s="6"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
+      <c r="A36" s="6"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
+      <c r="A37" s="6"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
+      <c r="A38" s="6"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7"/>
+      <c r="A39" s="6"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
+      <c r="A40" s="6"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7"/>
+      <c r="A41" s="6"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
+      <c r="A42" s="6"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7"/>
+      <c r="A43" s="6"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
+      <c r="A44" s="6"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7"/>
+      <c r="A45" s="6"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7"/>
+      <c r="A46" s="6"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7"/>
+      <c r="A47" s="6"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7"/>
+      <c r="A48" s="6"/>
       <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7"/>
+      <c r="A49" s="6"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
+      <c r="A50" s="6"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
+      <c r="A51" s="6"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
+      <c r="A52" s="6"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7"/>
+      <c r="A53" s="6"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
+      <c r="A54" s="6"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7"/>
+      <c r="A55" s="6"/>
       <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
+      <c r="A56" s="6"/>
       <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7"/>
+      <c r="A57" s="6"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7"/>
+      <c r="A58" s="6"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7"/>
+      <c r="A59" s="6"/>
       <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
+      <c r="A60" s="6"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7"/>
+      <c r="A61" s="6"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7"/>
+      <c r="A62" s="6"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7"/>
+      <c r="A63" s="6"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7"/>
+      <c r="A64" s="6"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
+      <c r="A65" s="6"/>
       <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
+      <c r="A66" s="6"/>
       <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7"/>
+      <c r="A67" s="6"/>
       <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7"/>
+      <c r="A68" s="6"/>
       <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7"/>
+      <c r="A69" s="6"/>
       <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7"/>
+      <c r="A70" s="6"/>
       <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7"/>
+      <c r="A71" s="6"/>
       <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7"/>
+      <c r="A72" s="6"/>
       <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7"/>
+      <c r="A73" s="6"/>
       <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7"/>
+      <c r="A74" s="6"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7"/>
+      <c r="A75" s="6"/>
       <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7"/>
+      <c r="A76" s="6"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7"/>
+      <c r="A77" s="6"/>
       <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7"/>
+      <c r="A78" s="6"/>
       <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7"/>
+      <c r="A79" s="6"/>
       <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7"/>
+      <c r="A80" s="6"/>
       <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7"/>
+      <c r="A81" s="6"/>
       <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7"/>
+      <c r="A82" s="6"/>
       <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7"/>
+      <c r="A83" s="6"/>
       <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7"/>
+      <c r="A84" s="6"/>
       <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7"/>
+      <c r="A85" s="6"/>
       <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7"/>
+      <c r="A86" s="6"/>
       <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7"/>
+      <c r="A87" s="6"/>
       <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7"/>
+      <c r="A88" s="6"/>
       <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7"/>
+      <c r="A89" s="6"/>
       <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7"/>
+      <c r="A90" s="6"/>
       <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7"/>
+      <c r="A91" s="6"/>
       <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7"/>
+      <c r="A92" s="6"/>
       <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7"/>
+      <c r="A93" s="6"/>
       <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7"/>
+      <c r="A94" s="6"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7"/>
+      <c r="A95" s="6"/>
       <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="7"/>
+      <c r="A96" s="6"/>
       <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7"/>
+      <c r="A97" s="6"/>
       <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7"/>
+      <c r="A98" s="6"/>
       <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7"/>
+      <c r="A99" s="6"/>
       <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="7"/>
+      <c r="A100" s="6"/>
       <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7"/>
+      <c r="A101" s="6"/>
       <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7"/>
+      <c r="A102" s="6"/>
       <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7"/>
+      <c r="A103" s="6"/>
       <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7"/>
+      <c r="A104" s="6"/>
       <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7"/>
+      <c r="A105" s="6"/>
       <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7"/>
+      <c r="A106" s="6"/>
       <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7"/>
+      <c r="A107" s="6"/>
       <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7"/>
+      <c r="A108" s="6"/>
       <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7"/>
+      <c r="A109" s="6"/>
       <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7"/>
+      <c r="A110" s="6"/>
       <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7"/>
+      <c r="A111" s="6"/>
       <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7"/>
+      <c r="A112" s="6"/>
       <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7"/>
+      <c r="A113" s="6"/>
       <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7"/>
+      <c r="A114" s="6"/>
       <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7"/>
+      <c r="A115" s="6"/>
       <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="7"/>
+      <c r="A116" s="6"/>
       <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7"/>
+      <c r="A117" s="6"/>
       <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7"/>
+      <c r="A118" s="6"/>
       <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7"/>
+      <c r="A119" s="6"/>
       <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7"/>
+      <c r="A120" s="6"/>
       <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7"/>
+      <c r="A121" s="6"/>
       <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="7"/>
+      <c r="A122" s="6"/>
       <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7"/>
+      <c r="A123" s="6"/>
       <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="7"/>
+      <c r="A124" s="6"/>
       <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="7"/>
+      <c r="A125" s="6"/>
       <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="7"/>
+      <c r="A126" s="6"/>
       <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="7"/>
+      <c r="A127" s="6"/>
       <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="7"/>
+      <c r="A128" s="6"/>
       <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="7"/>
+      <c r="A129" s="6"/>
       <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="7"/>
+      <c r="A130" s="6"/>
       <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="7"/>
+      <c r="A131" s="6"/>
       <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="7"/>
+      <c r="A132" s="6"/>
       <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="7"/>
+      <c r="A133" s="6"/>
       <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="7"/>
+      <c r="A134" s="6"/>
       <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="7"/>
+      <c r="A135" s="6"/>
       <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="7"/>
+      <c r="A136" s="6"/>
       <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="7"/>
+      <c r="A137" s="6"/>
       <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="7"/>
+      <c r="A138" s="6"/>
       <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="7"/>
+      <c r="A139" s="6"/>
       <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="7"/>
+      <c r="A140" s="6"/>
       <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="7"/>
+      <c r="A141" s="6"/>
       <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="7"/>
+      <c r="A142" s="6"/>
       <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7"/>
+      <c r="A143" s="6"/>
       <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="7"/>
+      <c r="A144" s="6"/>
       <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7"/>
+      <c r="A145" s="6"/>
       <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="7"/>
+      <c r="A146" s="6"/>
       <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7"/>
+      <c r="A147" s="6"/>
       <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="7"/>
+      <c r="A148" s="6"/>
       <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7"/>
+      <c r="A149" s="6"/>
       <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="7"/>
+      <c r="A150" s="6"/>
       <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="7"/>
+      <c r="A151" s="6"/>
       <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="7"/>
+      <c r="A152" s="6"/>
       <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="7"/>
+      <c r="A153" s="6"/>
       <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="7"/>
+      <c r="A154" s="6"/>
       <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="7"/>
+      <c r="A155" s="6"/>
       <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="7"/>
+      <c r="A156" s="6"/>
       <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="7"/>
+      <c r="A157" s="6"/>
       <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="7"/>
+      <c r="A158" s="6"/>
       <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="7"/>
+      <c r="A159" s="6"/>
       <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="7"/>
+      <c r="A160" s="6"/>
       <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="7"/>
+      <c r="A161" s="6"/>
       <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="7"/>
+      <c r="A162" s="6"/>
       <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7"/>
+      <c r="A163" s="6"/>
       <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="7"/>
+      <c r="A164" s="6"/>
       <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="7"/>
+      <c r="A165" s="6"/>
       <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="7"/>
+      <c r="A166" s="6"/>
       <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7"/>
+      <c r="A167" s="6"/>
       <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7"/>
+      <c r="A168" s="6"/>
       <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7"/>
+      <c r="A169" s="6"/>
       <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7"/>
+      <c r="A170" s="6"/>
       <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7"/>
+      <c r="A171" s="6"/>
       <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="7"/>
+      <c r="A172" s="6"/>
       <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7"/>
+      <c r="A173" s="6"/>
       <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="7"/>
+      <c r="A174" s="6"/>
       <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7"/>
+      <c r="A175" s="6"/>
       <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="7"/>
+      <c r="A176" s="6"/>
       <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7"/>
+      <c r="A177" s="6"/>
       <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="7"/>
+      <c r="A178" s="6"/>
       <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7"/>
+      <c r="A179" s="6"/>
       <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="7"/>
+      <c r="A180" s="6"/>
       <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7"/>
+      <c r="A181" s="6"/>
       <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7"/>
+      <c r="A182" s="6"/>
       <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7"/>
+      <c r="A183" s="6"/>
       <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="7"/>
+      <c r="A184" s="6"/>
       <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7"/>
+      <c r="A185" s="6"/>
       <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7"/>
+      <c r="A186" s="6"/>
       <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7"/>
+      <c r="A187" s="6"/>
       <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="7"/>
+      <c r="A188" s="6"/>
       <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7"/>
+      <c r="A189" s="6"/>
       <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7"/>
+      <c r="A190" s="6"/>
       <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7"/>
+      <c r="A191" s="6"/>
       <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="7"/>
+      <c r="A192" s="6"/>
       <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="7"/>
+      <c r="A193" s="6"/>
       <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="7"/>
+      <c r="A194" s="6"/>
       <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="7"/>
+      <c r="A195" s="6"/>
       <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="7"/>
+      <c r="A196" s="6"/>
       <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="7"/>
+      <c r="A197" s="6"/>
       <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="7"/>
+      <c r="A198" s="6"/>
       <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
+++ b/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Nachlassverzeichnis" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Ertrag Fisher Depot" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Ertrag comdirect 2025" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Beerdigungskosten" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t xml:space="preserve">Nachlasssache Klas Krüger</t>
   </si>
@@ -162,6 +163,15 @@
   </si>
   <si>
     <t xml:space="preserve">Übertrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trauerredner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cafe Deseo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bestatter Stolle</t>
   </si>
 </sst>
 </file>
@@ -1813,4 +1823,56 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.23"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="0" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>843.4</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>5478.75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="n">
+        <f aca="false">SUM(B1:B4)</f>
+        <v>6925.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
+++ b/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bk\bk_shared\klas\erbschaft\nachlass\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F18EED-B43A-4AF9-B17F-7ED046593480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Nachlassverzeichnis" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Ertrag Fisher Depot" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Ertrag comdirect 2025" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Beerdigungskosten" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Nachlassverzeichnis" sheetId="1" r:id="rId1"/>
+    <sheet name="Ertrag Fisher Depot" sheetId="2" r:id="rId2"/>
+    <sheet name="Ertrag comdirect 2025" sheetId="3" r:id="rId3"/>
+    <sheet name="Beerdigungskosten" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -23,27 +39,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
-  <si>
-    <t xml:space="preserve">Nachlasssache Klas Krüger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nachlassverzeichnis auf den Sterbetag 05.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wert per</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aktiva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depot Fisher Investments (KNR 1181314814)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depot comdirect 118 728563800, sonstiges</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+  <si>
+    <t>Nachlasssache Klas Krüger</t>
+  </si>
+  <si>
+    <t>Nachlassverzeichnis auf den Sterbetag 05.02.2026</t>
+  </si>
+  <si>
+    <t>Wert</t>
+  </si>
+  <si>
+    <t>Wert per</t>
+  </si>
+  <si>
+    <t>Aktiva</t>
+  </si>
+  <si>
+    <t>Depot Fisher Investments (KNR 1181314814)</t>
+  </si>
+  <si>
+    <t>Depot comdirect 118 728563800, sonstiges</t>
   </si>
   <si>
     <r>
@@ -62,146 +78,131 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5258263660</t>
+      <t>5258263660</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Summe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fisher Depot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fisher Depot Managementgebühren Q1-Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comdirect Depot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erträge 2025 gesamt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fisher Depot bis Q1-Q3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fisher Depot Managementgebühren Q1+Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(geschätzt wie 2025)</t>
+    <t>Summe</t>
+  </si>
+  <si>
+    <t>Fisher Depot</t>
+  </si>
+  <si>
+    <t>Fisher Depot Managementgebühren Q1-Q4</t>
+  </si>
+  <si>
+    <t>comdirect Depot</t>
+  </si>
+  <si>
+    <t>Erträge 2025 gesamt</t>
+  </si>
+  <si>
+    <t>Fisher Depot bis Q1-Q3</t>
+  </si>
+  <si>
+    <t>Fisher Depot Managementgebühren Q1+Q2</t>
+  </si>
+  <si>
+    <t>(geschätzt wie 2025)</t>
   </si>
   <si>
     <t xml:space="preserve">Erträge 2026 1.1-30.9. </t>
   </si>
   <si>
-    <t xml:space="preserve">Summe Einnahmen 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depotverwaltung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe Steuern 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q2/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ergebnis 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q4/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe Einnahmen 26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe Steuern 26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q2/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depoverwaltung 26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ergebnis 26 (Q1-Q3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basiert auf Finanzreports 01-12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Girokonto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tagesgeld</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verrechnung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depot</t>
+    <t>Summe Einnahmen 25</t>
+  </si>
+  <si>
+    <t>Depotverwaltung</t>
+  </si>
+  <si>
+    <t>Summe Steuern 25</t>
+  </si>
+  <si>
+    <t>Q1/2025</t>
+  </si>
+  <si>
+    <t>Q2/2025</t>
+  </si>
+  <si>
+    <t>Q3/2025</t>
+  </si>
+  <si>
+    <t>Ergebnis 25</t>
+  </si>
+  <si>
+    <t>Q4/2025</t>
+  </si>
+  <si>
+    <t>Summe Einnahmen 26</t>
+  </si>
+  <si>
+    <t>Q1/2026</t>
+  </si>
+  <si>
+    <t>Summe Steuern 26</t>
+  </si>
+  <si>
+    <t>Q2/2026</t>
+  </si>
+  <si>
+    <t>Depoverwaltung 26</t>
+  </si>
+  <si>
+    <t>Ergebnis 26 (Q1-Q3)</t>
+  </si>
+  <si>
+    <t>Basiert auf Finanzreports 01-12/2025</t>
+  </si>
+  <si>
+    <t>Girokonto</t>
+  </si>
+  <si>
+    <t>Tagesgeld</t>
+  </si>
+  <si>
+    <t>Verrechnung</t>
+  </si>
+  <si>
+    <t>Depot</t>
   </si>
   <si>
     <t xml:space="preserve">Ertragsgutschrift </t>
   </si>
   <si>
-    <t xml:space="preserve">Storno Ertragsgutschrift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zinsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übertrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trauerredner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cafe Deseo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bestatter Stolle</t>
+    <t>Storno Ertragsgutschrift</t>
+  </si>
+  <si>
+    <t>Zinsen</t>
+  </si>
+  <si>
+    <t>Übertrag</t>
+  </si>
+  <si>
+    <t>Trauerredner</t>
+  </si>
+  <si>
+    <t>Cafe Deseo</t>
+  </si>
+  <si>
+    <t>Bestatter Stolle</t>
+  </si>
+  <si>
+    <t>(Q3 Gebühren liegen noch nicht vor)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -210,7 +211,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -226,7 +227,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -234,70 +235,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -339,14 +305,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -399,163 +365,163 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>1325994.42</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>46058</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>111168.24</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>46058</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:3" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>1100</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="1">
         <v>46056</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="n">
-        <f aca="false">SUM(B5:B8)</f>
+      <c r="B9" s="2">
+        <f>SUM(B5:B8)</f>
         <v>1438262.66</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>16767</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="B13" s="3">
+        <v>16990.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>-14695.98</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15">
         <v>1413</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="2" t="n">
-        <f aca="false">SUM(B13:B16)</f>
-        <v>3484.02</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="B17" s="2">
+        <f>SUM(B13:B16)</f>
+        <v>3707.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21">
         <v>12502.3</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22">
         <v>-7787.65</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23">
         <v>1413</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="2" t="n">
-        <f aca="false">SUM(B21:B24)</f>
+      <c r="B25" s="2">
+        <f>SUM(B21:B24)</f>
         <v>6127.65</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Aptos,Standard"&amp;K0000ff Internal&amp;1#_x005F_x000D_&amp;"Times New Roman,Standard"&amp;12&amp;K000000&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
@@ -563,1094 +529,1074 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G198"/>
-  <sheetFormatPr defaultColWidth="10.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.29"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="3" t="n">
+      <c r="B1" s="3">
         <v>23548.63</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="3">
         <v>-6558.25</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2">
         <v>3458.18</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="0" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3">
         <v>3874.27</v>
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>3460.27</v>
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <f aca="false">SUM(B1:B4)</f>
+      <c r="B5">
+        <f>SUM(B1:B4)</f>
         <v>16990.38</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>3903.26</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E6" s="0" t="n">
-        <f aca="false">SUM(E2:E5)</f>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <f>SUM(E2:E5)</f>
         <v>14695.98</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>18442.41</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>3874.27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>-5940.11</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9">
         <v>3913.38</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="0" t="n">
-        <f aca="false">SUM(E8:E9)</f>
+      <c r="E10">
+        <f>SUM(E8:E9)</f>
         <v>7787.65</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <f aca="false">SUM(B8:B11)</f>
+      <c r="B12">
+        <f>SUM(B8:B11)</f>
         <v>12502.3</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" s="5"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="10.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="n">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B2" s="1">
         <v>45657</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>45691</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="1">
         <v>45719</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="1">
         <v>45748</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="1">
         <v>45779</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45810</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="1">
         <v>45840</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="1">
         <v>45870</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="1">
         <v>45901</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="1">
         <v>45932</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="1">
         <v>45964</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="1">
         <v>45992</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="1">
         <v>46022</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3">
         <v>10848</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3">
         <v>11198</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3">
         <v>12554</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3">
         <v>14307</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3">
         <v>15933</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3">
         <v>17072</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>17913</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3">
         <v>19365</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3">
         <v>20736</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3">
         <v>22166</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3">
         <v>24386</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3">
         <v>25810</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3">
         <v>28009</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>25099</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4">
         <v>25099</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>25099</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>25133</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4">
         <v>25133</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4">
         <v>25133</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4">
         <v>25167</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4">
         <v>25167</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4">
         <v>25167</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4">
         <v>25201</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4">
         <v>25201</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4">
         <v>25201</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4">
         <v>25235</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>3915</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5">
         <v>3915</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5">
         <v>3915</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>4053</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5">
         <v>4332</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5">
         <v>4825</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5">
         <v>5029</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5">
         <v>5029</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5">
         <v>5029</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5">
         <v>5162</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5">
         <v>5162</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5">
         <v>5162</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5">
         <v>5162</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>51751</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6">
         <v>55456</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6">
         <v>59361</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>57574</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6">
         <v>56166</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>56634</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>54819</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6">
         <v>51790</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6">
         <v>53118</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6">
         <v>53506</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6">
         <v>53626</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6">
         <v>56646</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6">
         <v>57560</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>45748</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>273</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>45772</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11">
         <v>278</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>45789</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12">
         <v>294</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>45804</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13">
         <v>-278</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>45805</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>278</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>45807</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15">
         <v>198</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>45838</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16">
         <v>34</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>45831</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17">
         <v>204</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>45919</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18">
         <v>132</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="0" t="n">
-        <f aca="false">SUM(B10:B19)</f>
+      <c r="B20">
+        <f>SUM(B10:B19)</f>
         <v>1413</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.29"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="0" t="n">
+      <c r="B1">
         <v>603</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2">
         <v>843.4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3">
         <v>5478.75</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
-        <f aca="false">SUM(B1:B4)</f>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <f>SUM(B1:B4)</f>
         <v>6925.15</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>

--- a/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
+++ b/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bk\bk_shared\klas\erbschaft\nachlass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D6C4B3F170A4B06DDBCE5B378F82F9B35D00F821" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBB85D7-CA7B-4B4F-B36E-8BCC511794A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="270" windowWidth="28800" windowHeight="14370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="10410" windowWidth="38400" windowHeight="10470" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nachlassverzeichnis" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>Nachlasssache Klas Krüger</t>
   </si>
@@ -62,24 +59,7 @@
     <t>Depot comdirect 118 728563800, sonstiges</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Geschäftseinlage green-planetengergy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>5258263660</t>
-    </r>
+    <t>Geschäftseinlage green-planetengergy 5258263660</t>
   </si>
   <si>
     <t>50% LZO Konto</t>
@@ -100,6 +80,9 @@
     <t>comdirect Depot</t>
   </si>
   <si>
+    <t>(aus Blatt 'Ertrag comdirect 2025', korrigiert 20.10.2026)</t>
+  </si>
+  <si>
     <t>Erträge 2025 gesamt</t>
   </si>
   <si>
@@ -175,16 +158,40 @@
     <t>Depot</t>
   </si>
   <si>
-    <t xml:space="preserve">Ertragsgutschrift </t>
-  </si>
-  <si>
-    <t>Storno Ertragsgutschrift</t>
-  </si>
-  <si>
-    <t>Zinsen</t>
-  </si>
-  <si>
-    <t>Übertrag</t>
+    <t>Zinsen Tagesgeld Q1 (netto)</t>
+  </si>
+  <si>
+    <t>Ertragsgutschrift Roche (netto)</t>
+  </si>
+  <si>
+    <t>Ertragsgutschrift Nestlé (netto)</t>
+  </si>
+  <si>
+    <t>Ertragsgutschrift Fuchs (netto)</t>
+  </si>
+  <si>
+    <t>Storno Ertragsgutschrift Nestlé</t>
+  </si>
+  <si>
+    <t>Ertragsgutschrift Nestlé neu (netto)</t>
+  </si>
+  <si>
+    <t>Ertragsgutschrift Reckitt (netto)</t>
+  </si>
+  <si>
+    <t>Steuererstattung (Übertrag GS-OPS TAX QUEST)</t>
+  </si>
+  <si>
+    <t>Zinsen Tagesgeld Q2 (netto)</t>
+  </si>
+  <si>
+    <t>Zinsen Tagesgeld Q3 (netto)</t>
+  </si>
+  <si>
+    <t>Zinsen Tagesgeld Q4 (netto)</t>
+  </si>
+  <si>
+    <t>Korrigiert 20.10.2026: exakte Centbeträge aus den Finanzreporten; Tagesgeldzinsen Q1, Q3, Q4 ergänzt (bisher nur Q2).</t>
   </si>
   <si>
     <t>Trauerredner</t>
@@ -203,15 +210,9 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -247,9 +248,9 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,7 +430,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -494,22 +495,26 @@
       <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17">
-        <v>1413</v>
+      <c r="B17" s="3">
+        <f>'Ertrag comdirect 2025'!B23</f>
+        <v>1517.63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4">
         <f>SUM(B15:B18)</f>
-        <v>3707.41</v>
+        <v>3812.04</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23">
         <v>12502.3</v>
@@ -517,41 +522,42 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>-7787.65</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>13</v>
       </c>
-      <c r="B25">
-        <v>1413</v>
+      <c r="B25" s="3">
+        <f>'Ertrag comdirect 2025'!B23</f>
+        <v>1517.63</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="2">
+        <v>20</v>
+      </c>
+      <c r="B27" s="4">
         <f>SUM(B23:B26)</f>
-        <v>6127.65</v>
+        <v>6232.28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos,Standard"&amp;K0000ff Internal&amp;1#_x005F_x000D_&amp;"Times New Roman,Standard"&amp;12&amp;K000000&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Aptos,Standard"&amp;K0000ff Internal&amp;1#_x000D_&amp;"Times New Roman,Standard"&amp;12 &amp;K000000&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12 Seite &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -569,24 +575,24 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3">
         <v>23548.63</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3">
         <v>-6558.25</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>3458.18</v>
@@ -594,7 +600,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>3874.27</v>
@@ -604,7 +610,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>3460.27</v>
@@ -613,14 +619,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <f>SUM(B1:B4)</f>
         <v>16990.38</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>3903.26</v>
@@ -634,13 +640,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>18442.41</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>3874.27</v>
@@ -648,13 +654,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9">
         <v>-5940.11</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>3913.38</v>
@@ -662,7 +668,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10">
         <f>SUM(E8:E9)</f>
@@ -674,7 +680,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <f>SUM(B8:B11)</f>
@@ -1244,12 +1250,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -1295,7 +1301,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>10848</v>
@@ -1339,7 +1345,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>25099</v>
@@ -1383,7 +1389,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>3915</v>
@@ -1427,7 +1433,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>51751</v>
@@ -1471,110 +1477,148 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>45748</v>
-      </c>
-      <c r="B10">
-        <v>273</v>
+        <v>45747</v>
+      </c>
+      <c r="B10" s="3">
+        <v>33.89</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>45772</v>
-      </c>
-      <c r="B11">
-        <v>278</v>
+        <v>45748</v>
+      </c>
+      <c r="B11" s="3">
+        <v>273.02</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>45789</v>
-      </c>
-      <c r="B12">
-        <v>294</v>
+        <v>45772</v>
+      </c>
+      <c r="B12" s="3">
+        <v>278.7</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>45804</v>
-      </c>
-      <c r="B13">
-        <v>-278</v>
+        <v>45789</v>
+      </c>
+      <c r="B13" s="3">
+        <v>294.87</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>45805</v>
-      </c>
-      <c r="B14">
-        <v>278</v>
+        <v>45804</v>
+      </c>
+      <c r="B14" s="3">
+        <v>-278.7</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>45807</v>
-      </c>
-      <c r="B15">
-        <v>198</v>
+        <v>45805</v>
+      </c>
+      <c r="B15" s="3">
+        <v>278.7</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B16">
-        <v>34</v>
+        <v>45807</v>
+      </c>
+      <c r="B16" s="3">
+        <v>198.27</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>45831</v>
       </c>
-      <c r="B17">
-        <v>204</v>
+      <c r="B17" s="3">
+        <v>204.23</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B18" s="3">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>45919</v>
       </c>
-      <c r="B18">
-        <v>132</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
+      <c r="B19" s="3">
+        <v>132.66999999999999</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B20" s="3">
+        <v>33.99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B21" s="3">
+        <v>34.04</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>10</v>
       </c>
-      <c r="B20">
-        <f>SUM(B10:B19)</f>
-        <v>1413</v>
+      <c r="B23" s="3">
+        <f>SUM(B10:B21)</f>
+        <v>1517.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1593,7 +1637,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B1">
         <v>603</v>
@@ -1601,7 +1645,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>843.4</v>
@@ -1609,7 +1653,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>5478.75</v>
@@ -1625,8 +1669,8 @@
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12 Seite &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
+++ b/klas/erbschaft/nachlass/Nachlass_klas_krueger.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bk\bk_shared\klas\erbschaft\nachlass\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBB85D7-CA7B-4B4F-B36E-8BCC511794A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="10410" windowWidth="38400" windowHeight="10470" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Nachlassverzeichnis" sheetId="1" r:id="rId1"/>
-    <sheet name="Ertrag Fisher Depot" sheetId="2" r:id="rId2"/>
-    <sheet name="Ertrag comdirect 2025" sheetId="3" r:id="rId3"/>
-    <sheet name="Beerdigungskosten" sheetId="4" r:id="rId4"/>
+    <sheet name="Nachlassverzeichnis" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Ertrag Fisher Depot" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Ertrag comdirect 2025" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Beerdigungskosten" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -38,179 +25,182 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
-    <t>Nachlasssache Klas Krüger</t>
-  </si>
-  <si>
-    <t>Nachlassverzeichnis auf den Sterbetag 05.02.2026</t>
-  </si>
-  <si>
-    <t>Wert</t>
-  </si>
-  <si>
-    <t>Wert per</t>
-  </si>
-  <si>
-    <t>Aktiva</t>
-  </si>
-  <si>
-    <t>Depot Fisher Investments (KNR 1181314814)</t>
-  </si>
-  <si>
-    <t>Depot comdirect 118 728563800, sonstiges</t>
-  </si>
-  <si>
-    <t>Geschäftseinlage green-planetengergy 5258263660</t>
-  </si>
-  <si>
-    <t>50% LZO Konto</t>
-  </si>
-  <si>
-    <t>50% Lohnsteuerjahresausgleich 24/25</t>
-  </si>
-  <si>
-    <t>Summe</t>
-  </si>
-  <si>
-    <t>Fisher Depot</t>
-  </si>
-  <si>
-    <t>Fisher Depot Managementgebühren Q1-Q4</t>
-  </si>
-  <si>
-    <t>comdirect Depot</t>
-  </si>
-  <si>
-    <t>(aus Blatt 'Ertrag comdirect 2025', korrigiert 20.10.2026)</t>
-  </si>
-  <si>
-    <t>Erträge 2025 gesamt</t>
-  </si>
-  <si>
-    <t>Fisher Depot bis Q1-Q3</t>
-  </si>
-  <si>
-    <t>Fisher Depot Managementgebühren Q1+Q2</t>
-  </si>
-  <si>
-    <t>(Q3 Gebühren liegen noch nicht vor)</t>
-  </si>
-  <si>
-    <t>(geschätzt wie 2025)</t>
+    <t xml:space="preserve">Nachlasssache Klas Krüger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nachlassverzeichnis auf den Sterbetag 05.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wert per</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktiva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depot Fisher Investments (KNR 1181314814)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depot comdirect 118 728563800, sonstiges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geschäftseinlage green-planetengergy 5258263660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% LZO Konto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% Lohnsteuerjahresausgleich 24/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fisher Depot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fisher Depot Managementgebühren Q1-Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comdirect Depot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(aus Blatt 'Ertrag comdirect 2025', korrigiert 20.10.2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erträge 2025 gesamt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fisher Depot bis Q1-Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fisher Depot Managementgebühren Q1+Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Q3 Gebühren liegen noch nicht vor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(geschätzt wie 2025)</t>
   </si>
   <si>
     <t xml:space="preserve">Erträge 2026 1.1-30.9. </t>
   </si>
   <si>
-    <t>Summe Einnahmen 25</t>
-  </si>
-  <si>
-    <t>Depotverwaltung</t>
-  </si>
-  <si>
-    <t>Summe Steuern 25</t>
-  </si>
-  <si>
-    <t>Q1/2025</t>
-  </si>
-  <si>
-    <t>Q2/2025</t>
-  </si>
-  <si>
-    <t>Q3/2025</t>
-  </si>
-  <si>
-    <t>Ergebnis 25</t>
-  </si>
-  <si>
-    <t>Q4/2025</t>
-  </si>
-  <si>
-    <t>Summe Einnahmen 26</t>
-  </si>
-  <si>
-    <t>Q1/2026</t>
-  </si>
-  <si>
-    <t>Summe Steuern 26</t>
-  </si>
-  <si>
-    <t>Q2/2026</t>
-  </si>
-  <si>
-    <t>Depoverwaltung 26</t>
-  </si>
-  <si>
-    <t>Ergebnis 26 (Q1-Q3)</t>
-  </si>
-  <si>
-    <t>Basiert auf Finanzreports 01-12/2025</t>
-  </si>
-  <si>
-    <t>Girokonto</t>
-  </si>
-  <si>
-    <t>Tagesgeld</t>
-  </si>
-  <si>
-    <t>Verrechnung</t>
-  </si>
-  <si>
-    <t>Depot</t>
-  </si>
-  <si>
-    <t>Zinsen Tagesgeld Q1 (netto)</t>
-  </si>
-  <si>
-    <t>Ertragsgutschrift Roche (netto)</t>
-  </si>
-  <si>
-    <t>Ertragsgutschrift Nestlé (netto)</t>
-  </si>
-  <si>
-    <t>Ertragsgutschrift Fuchs (netto)</t>
-  </si>
-  <si>
-    <t>Storno Ertragsgutschrift Nestlé</t>
-  </si>
-  <si>
-    <t>Ertragsgutschrift Nestlé neu (netto)</t>
-  </si>
-  <si>
-    <t>Ertragsgutschrift Reckitt (netto)</t>
-  </si>
-  <si>
-    <t>Steuererstattung (Übertrag GS-OPS TAX QUEST)</t>
-  </si>
-  <si>
-    <t>Zinsen Tagesgeld Q2 (netto)</t>
-  </si>
-  <si>
-    <t>Zinsen Tagesgeld Q3 (netto)</t>
-  </si>
-  <si>
-    <t>Zinsen Tagesgeld Q4 (netto)</t>
-  </si>
-  <si>
-    <t>Korrigiert 20.10.2026: exakte Centbeträge aus den Finanzreporten; Tagesgeldzinsen Q1, Q3, Q4 ergänzt (bisher nur Q2).</t>
-  </si>
-  <si>
-    <t>Trauerredner</t>
-  </si>
-  <si>
-    <t>Cafe Deseo</t>
-  </si>
-  <si>
-    <t>Bestatter Stolle</t>
+    <t xml:space="preserve">Summe Einnahmen 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depotverwaltung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Steuern 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ergebnis 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Einnahmen 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Steuern 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depoverwaltung 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ergebnis 26 (Q1-Q3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basiert auf Finanzreports 01-12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Girokonto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tagesgeld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verrechnung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinsen Tagesgeld Q1 (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ertragsgutschrift Roche (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ertragsgutschrift Nestlé (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ertragsgutschrift Fuchs (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storno Ertragsgutschrift Nestlé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ertragsgutschrift Nestlé neu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ertragsgutschrift Reckitt (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steuererstattung (Übertrag GS-OPS TAX QUEST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinsen Tagesgeld Q2 (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinsen Tagesgeld Q3 (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zinsen Tagesgeld Q4 (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korrigiert 20.10.2026: exakte Centbeträge aus den Finanzreporten; Tagesgeldzinsen Q1, Q3, Q4 ergänzt (bisher nur Q2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trauerredner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cafe Deseo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bestatter Stolle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -218,7 +208,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -234,7 +239,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -242,35 +247,70 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -312,14 +352,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -372,1303 +412,1325 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0" t="n">
         <v>1325994.42</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>46058</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0" t="n">
         <v>111168.24</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="1" t="n">
         <v>46058</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0" t="n">
         <v>1100</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="n">
         <v>46056</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0" t="n">
         <v>3288.77</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>46058</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0" t="n">
         <v>3416.13</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="n">
         <v>46310</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <f>SUM(B5:B9)</f>
-        <v>1444967.5599999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="n">
+        <f aca="false">SUM(B5:B9)</f>
+        <v>1444967.56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="3" t="n">
         <v>16990.39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="0" t="n">
         <v>-14695.98</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="3">
-        <f>'Ertrag comdirect 2025'!B23</f>
+      <c r="B17" s="3" t="n">
+        <f aca="false">'Ertrag comdirect 2025'!B23</f>
         <v>1517.63</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="4">
-        <f>SUM(B15:B18)</f>
+      <c r="B19" s="4" t="n">
+        <f aca="false">SUM(B15:B18)</f>
         <v>3812.04</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="0" t="n">
         <v>12502.3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="0" t="n">
         <v>-7787.65</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="0" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="3">
-        <f>'Ertrag comdirect 2025'!B23</f>
+      <c r="B25" s="3" t="n">
+        <f aca="false">'Ertrag comdirect 2025'!B23</f>
         <v>1517.63</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="0" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="4">
-        <f>SUM(B23:B26)</f>
+      <c r="B27" s="4" t="n">
+        <f aca="false">SUM(B23:B26)</f>
         <v>6232.28</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos,Standard"&amp;K0000ff Internal&amp;1#_x000D_&amp;"Times New Roman,Standard"&amp;12 &amp;K000000&amp;A</oddHeader>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Aptos,Standard"&amp;K0000ff Internal&amp;1#_x005F_x000D_&amp;"Times New Roman,Standard"&amp;12 &amp;K000000&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12 Seite &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G198"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="3" t="n">
         <v>23548.63</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="3" t="n">
         <v>-6558.25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0" t="n">
         <v>3458.18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D3" t="s">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D3" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0" t="n">
         <v>3874.27</v>
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4"/>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0" t="n">
         <v>3460.27</v>
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B5">
-        <f>SUM(B1:B4)</f>
+      <c r="B5" s="0" t="n">
+        <f aca="false">SUM(B1:B4)</f>
         <v>16990.38</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0" t="n">
         <v>3903.26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E6">
-        <f>SUM(E2:E5)</f>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E6" s="0" t="n">
+        <f aca="false">SUM(E2:E5)</f>
         <v>14695.98</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0" t="n">
         <v>18442.41</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="0" t="n">
         <v>3874.27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0" t="n">
         <v>-5940.11</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="0" t="n">
         <v>3913.38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E10">
-        <f>SUM(E8:E9)</f>
+      <c r="E10" s="0" t="n">
+        <f aca="false">SUM(E8:E9)</f>
         <v>7787.65</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B12">
-        <f>SUM(B8:B11)</f>
+      <c r="B12" s="0" t="n">
+        <f aca="false">SUM(B8:B11)</f>
         <v>12502.3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B2" s="1">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="n">
         <v>45691</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="1" t="n">
         <v>45719</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="n">
         <v>45748</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="1" t="n">
         <v>45779</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45810</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="1" t="n">
         <v>45840</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="1" t="n">
         <v>45870</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="1" t="n">
         <v>45901</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="1" t="n">
         <v>45932</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="1" t="n">
         <v>45964</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0" t="n">
         <v>10848</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>11198</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0" t="n">
         <v>12554</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0" t="n">
         <v>14307</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0" t="n">
         <v>15933</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0" t="n">
         <v>17072</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0" t="n">
         <v>17913</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="0" t="n">
         <v>19365</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="0" t="n">
         <v>20736</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="0" t="n">
         <v>22166</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="0" t="n">
         <v>24386</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="0" t="n">
         <v>25810</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="0" t="n">
         <v>28009</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0" t="n">
         <v>25099</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>25099</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0" t="n">
         <v>25099</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0" t="n">
         <v>25133</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="0" t="n">
         <v>25133</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="0" t="n">
         <v>25133</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0" t="n">
         <v>25167</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="0" t="n">
         <v>25167</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="0" t="n">
         <v>25167</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="0" t="n">
         <v>25201</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="0" t="n">
         <v>25201</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0" t="n">
         <v>25201</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="0" t="n">
         <v>25235</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0" t="n">
         <v>3915</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0" t="n">
         <v>3915</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0" t="n">
         <v>3915</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0" t="n">
         <v>4053</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0" t="n">
         <v>4332</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="0" t="n">
         <v>4825</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0" t="n">
         <v>5029</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="0" t="n">
         <v>5029</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="0" t="n">
         <v>5029</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="0" t="n">
         <v>5162</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="0" t="n">
         <v>5162</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="0" t="n">
         <v>5162</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="0" t="n">
         <v>5162</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0" t="n">
         <v>51751</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>55456</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0" t="n">
         <v>59361</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0" t="n">
         <v>57574</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0" t="n">
         <v>56166</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="0" t="n">
         <v>56634</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0" t="n">
         <v>54819</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="0" t="n">
         <v>51790</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0" t="n">
         <v>53118</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="0" t="n">
         <v>53506</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="0" t="n">
         <v>53626</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="0" t="n">
         <v>56646</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="0" t="n">
         <v>57560</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="3" t="n">
         <v>33.89</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>45748</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="3" t="n">
         <v>273.02</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>45772</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="3" t="n">
         <v>278.7</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>45789</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="3" t="n">
         <v>294.87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>45804</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="3" t="n">
         <v>-278.7</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>45805</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="3" t="n">
         <v>278.7</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
         <v>45807</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="3" t="n">
         <v>198.27</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
         <v>45831</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="3" t="n">
         <v>204.23</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="B18" s="3">
-        <v>33.950000000000003</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="3" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="B19" s="3">
-        <v>132.66999999999999</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="3" t="n">
+        <v>132.67</v>
+      </c>
+      <c r="C19" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="3" t="n">
         <v>33.99</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="0" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="3" t="n">
         <v>34.04</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="3">
-        <f>SUM(B10:B21)</f>
+      <c r="B23" s="3" t="n">
+        <f aca="false">SUM(B10:B21)</f>
         <v>1517.63</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="0" t="n">
         <v>603</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0" t="n">
         <v>843.4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0" t="n">
         <v>5478.75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <f>SUM(B1:B4)</f>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="n">
+        <f aca="false">SUM(B1:B4)</f>
         <v>6925.15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12 Seite &amp;P</oddFooter>
   </headerFooter>
